--- a/Workflows/Chemical validation/Level0_Templates/XXXX_XX_CATIONS.xlsx
+++ b/Workflows/Chemical validation/Level0_Templates/XXXX_XX_CATIONS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnun365-my.sharepoint.com/personal/jtorrens_unav_es/Documents/Documentos/LICA/data/plantillas/Forest/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\Level0_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{AE7C82AE-8C8D-4882-9E7D-A823FAA85301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F78F9734-972A-469F-B054-96975445900E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F350EEA7-2332-4349-BC0B-231B3D58352C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>SiteName</t>
   </si>
@@ -47,213 +47,6 @@
   </si>
   <si>
     <t>SampleID</t>
-  </si>
-  <si>
-    <t>05PS INT</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Valsain</t>
-  </si>
-  <si>
-    <t>05PS INT NIEVE</t>
-  </si>
-  <si>
-    <t>05PS INT LIX 20</t>
-  </si>
-  <si>
-    <t>05PS INT LIX 60</t>
-  </si>
-  <si>
-    <t>05PS INT LIX G 20</t>
-  </si>
-  <si>
-    <t>05PS INT LIX G 60</t>
-  </si>
-  <si>
-    <t>05PS EXT</t>
-  </si>
-  <si>
-    <t>05PS EXT NIEVE</t>
-  </si>
-  <si>
-    <t>06QI INT</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Morella</t>
-  </si>
-  <si>
-    <t>06QI EXT</t>
-  </si>
-  <si>
-    <t>07QI INT</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Majadas</t>
-  </si>
-  <si>
-    <t>07QI EXT</t>
-  </si>
-  <si>
-    <t>10PPA INT</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Almonte</t>
-  </si>
-  <si>
-    <t>10PPA EXT</t>
-  </si>
-  <si>
-    <t>11QS INT</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Villanueva de la Sierra</t>
-  </si>
-  <si>
-    <t>11QS EXT</t>
-  </si>
-  <si>
-    <t>22PN INT</t>
-  </si>
-  <si>
-    <t>Mora de Rubielos</t>
-  </si>
-  <si>
-    <t>22PN INT NIEVE</t>
-  </si>
-  <si>
-    <t>22PN EXT</t>
-  </si>
-  <si>
-    <t>22PN EXT NIEVE</t>
-  </si>
-  <si>
-    <t>25PH INT</t>
-  </si>
-  <si>
-    <t>Tibi</t>
-  </si>
-  <si>
-    <t>25PH EXT</t>
-  </si>
-  <si>
-    <t>26QI INT</t>
-  </si>
-  <si>
-    <t>Andujar</t>
-  </si>
-  <si>
-    <t>26QI EXT</t>
-  </si>
-  <si>
-    <t>30PS INT</t>
-  </si>
-  <si>
-    <t>Soria</t>
-  </si>
-  <si>
-    <t>30PS INT NIEVE</t>
-  </si>
-  <si>
-    <t>30PS INT LIX 20</t>
-  </si>
-  <si>
-    <t>30PS INT LIX 60</t>
-  </si>
-  <si>
-    <t>30PS EXT</t>
-  </si>
-  <si>
-    <t>30PS EXT NIEVE</t>
-  </si>
-  <si>
-    <t>33QPE INT</t>
-  </si>
-  <si>
-    <t>Cervera de Pisuerga</t>
-  </si>
-  <si>
-    <t>33QPE INT NIEVE</t>
-  </si>
-  <si>
-    <t>33QPE INT LIX 20</t>
-  </si>
-  <si>
-    <t>33QPE INT LIX 60</t>
-  </si>
-  <si>
-    <t>33QPE EXT</t>
-  </si>
-  <si>
-    <t>33QPE EXT NIEVE</t>
-  </si>
-  <si>
-    <t>37PPR INT</t>
-  </si>
-  <si>
-    <t>Cuellar</t>
-  </si>
-  <si>
-    <t>37PPR EXT</t>
-  </si>
-  <si>
-    <t>54PH INT</t>
-  </si>
-  <si>
-    <t>El Saler</t>
-  </si>
-  <si>
-    <t>54PH EXT</t>
-  </si>
-  <si>
-    <t>102PPR INT</t>
-  </si>
-  <si>
-    <t>Padron</t>
-  </si>
-  <si>
-    <t>102PPR INT LIX 20</t>
-  </si>
-  <si>
-    <t>102PPR INT LIX 60</t>
-  </si>
-  <si>
-    <t>102PPR EXT</t>
-  </si>
-  <si>
-    <t>115FS INT</t>
-  </si>
-  <si>
-    <t>Burguete</t>
-  </si>
-  <si>
-    <t>115FS INT NIEVE</t>
-  </si>
-  <si>
-    <t>115FS INT LIX 20</t>
-  </si>
-  <si>
-    <t>115FS INT LIX 60</t>
-  </si>
-  <si>
-    <t>115FS EXT</t>
-  </si>
-  <si>
-    <t>115FS EXT NIEVE</t>
   </si>
   <si>
     <t>Comments</t>
@@ -431,13 +224,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:rowOff>76198</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -452,8 +245,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="95250" y="76199"/>
-          <a:ext cx="12011025" cy="8620126"/>
+          <a:off x="95250" y="76198"/>
+          <a:ext cx="12011025" cy="21050252"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -491,115 +284,135 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="sng"/>
-            <a:t>PLANTILLA CATIONS</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>Esto es la plantilla (XXXX_12_ES02_CATIONS.xlsx) para </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>rellenar los datos de CATIONES en la hoja data</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>. Para cada año y mes se debe rellenar la plantilla una vez. Es IMPORTANTE nombrar la plantilla con el año y mes que corresponden, cambiando las XXXX_XX por el año_mes</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>en cuestión (ej: 2023_02_ES02_CATIONS.xlsx). La idea es copiar en esta plantilla los datos que se han logrado en el laboratorio. No es necesario eliminar ninguna fila, y si falta un dato o se ha obtenido un dato erróneo, no añadirlo y dejar la celda vacía.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>Columnas:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>SampleID</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: identificador único para los diferentes puntos de muestreo en las parcelas de estudio en la región de muestreo. Cada parcela corresponde a un subprograma de ICPIM.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>SiteName</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: nombre de donde se encuentran las muestras de trabajo.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>PlotCode</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: codigo de la zona donde se encuentran las muestras de trabajo.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>ScodeICPIM</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: codigo del tipo de parcela. Este codigo tambien corresponde al subprograma, ya que cada tipo de parcela corresponde a un subpograma de ICPIM diferente.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>EndDate</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: fecha del día en el que se ha recogido la muestra. Formato: dd/mm/YYYY</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>CA(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>Ca calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>MG(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>Mg calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>TEMPLATE: XXXX_XX_CATIONS.xlsx</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PURPOSE:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>This template records major cation and trace metal concentrations in water samples. One row per analytical sample.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FILE NAMING CONVENTION:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>YYYY_MM_CATIONS.xlsx     — original analysis</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>YYYY_MM_CATIONS_REP.xlsx — repeated analysis</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -621,648 +434,3363 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>NA(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Na calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>K(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>K calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>AL(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Al calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>FE(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Fe calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>MN(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Mn calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>AS(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>As calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>CD(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Cd calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>CR(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="0" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>C</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>r calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>CU(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Cu calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>MO(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Mo calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>NI(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Ni calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>PB(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Pb calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>ZN(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Zn calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>P(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>P calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>S(µg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>S calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>En este caso se realiza una plantillla para año y mes, logrando así 12 plantillas.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>MUCHAS GRACIAS POR EL ESFUERZO Y COLABORACIÓN!!</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>CUALQUIER DUDA NO DUDEIS EN PREGUNTARME (jtorrens@unav.es)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" b="0" u="none" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" b="1" u="none" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Where YYYY = year, MM = month of collection. If differente years or months are collected in the same template, you could</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>keep XX.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>COLUMNS:</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SampleID</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Unique identifier for the analytical sample. This is the key that links this template to all other templates and to the samplesInfo.xlsx metadata file.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>05PS INT, 22PN EXT NIEVE, 30PS INT LIX 20, 115FS EXT</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty. Must be identical across all templates for the same sample in the same month.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SiteCode</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Numeric code identifying the monitoring plot.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>05, 06, 22, 102, 115</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SiteName</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Name of the monitoring plot or location.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the official name of the plot (e.g. Valsain, Bertiz).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Valsain, Mora de Rubielos, Burguete</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>StartDate</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Date on which sample collection began (start of the accumulation period for the collector).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Format DD/MM/YYYY. Leave empty if not recorded.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>01/01/2025, 15/03/2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>EndDate</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Date on which sample collection ended (date the collector was retrieved and the sample taken to the lab).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Format DD/MM/YYYY.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>31/01/2025, 28/02/2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>year</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Year of collection (integer).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Four-digit year. Must match the YYYY in the filename.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2024, 2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>month</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Month of collection (integer, 1–12).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Numeric month without leading zero.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1, 6, 12</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CA(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Calcium concentration in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Enter the numeric value. Major cation, typically the most abundant in European precipitation chemistry.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.66, 1.20, 0.15</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>MG(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" i="0" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Magnesium concentration in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.14, 0.30</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>NA(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sodium concentration in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Major cation. Elevated Na is typically of marine origin.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.85, 2.10</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>K(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Potassium concentration in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.89, 0.40</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>AL(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Aluminium concentration in mg/L. Important indicator of soil acidification in throughfall and soil water.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.018, 0.05</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FE(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Iron concentration in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.006, 0.02</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>MN(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Manganese concentration in mg/L.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.028, 0.01</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>AS(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Arsenic concentration in mg/L. Trace element. Concentrations are typically in the µg/L range — enter in mg/L (e.g. 25 µg/L = 0.000025 mg/L).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000025, 0.000010</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CD(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cadmium concentration in mg/L. Trace element.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000008, 0.000003</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CR(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Chromium concentration in mg/L. Trace element.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000037, 0.000020</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CU(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Copper concentration in mg/L. Trace element.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000062, 0.000030</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CO(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cobalt concentration in mg/L. Trace element.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000010, 0.000005</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>NI(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Nickel concentration in mg/L. Trace element.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000073, 0.000040</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PB(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Lead concentration in mg/L. Trace element.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000011, 0.000008</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ZN(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Zinc concentration in mg/L. Trace element.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.000049, 0.000100</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>P(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Total phosphorus concentration in mg/L (elemental P, not as PO4).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.017, 0.010</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>S(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Total sulphur concentration in mg/L (elemental S, not as SO4).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.50, 0.25</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Comments</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Free-text field for any relevant observation about this sample.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Note any anomalies, collection issues, or observations that may affect data interpretation (e.g. "collector contaminated", "sample collected one week late", "snow sample mixed with rain"). Leave empty if nothing to report.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1568,7 +4096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1DD1C9D-C8E5-4B60-A994-86B75D81D72C}">
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="11.42578125" style="1"/>
@@ -2492,9 +5020,1320 @@
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
     </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7"/>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="7"/>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="7"/>
+      <c r="O58" s="7"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="7"/>
+      <c r="O61" s="7"/>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="7"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
+      <c r="N64" s="7"/>
+      <c r="O64" s="7"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
+      <c r="M65" s="7"/>
+      <c r="N65" s="7"/>
+      <c r="O65" s="7"/>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
+      <c r="N66" s="7"/>
+      <c r="O66" s="7"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
+      <c r="N68" s="7"/>
+      <c r="O68" s="7"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
+      <c r="N69" s="7"/>
+      <c r="O69" s="7"/>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
+      <c r="N70" s="7"/>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
+      <c r="M71" s="7"/>
+      <c r="N71" s="7"/>
+      <c r="O71" s="7"/>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7"/>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
+      <c r="M76" s="7"/>
+      <c r="N76" s="7"/>
+      <c r="O76" s="7"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+      <c r="M78" s="7"/>
+      <c r="N78" s="7"/>
+      <c r="O78" s="7"/>
+      <c r="P78" s="7"/>
+      <c r="Q78" s="7"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+      <c r="M79" s="7"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="7"/>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="7"/>
+      <c r="N80" s="7"/>
+      <c r="O80" s="7"/>
+      <c r="P80" s="7"/>
+      <c r="Q80" s="7"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="7"/>
+      <c r="O81" s="7"/>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+      <c r="Q82" s="7"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
+      <c r="M83" s="7"/>
+      <c r="N83" s="7"/>
+      <c r="O83" s="7"/>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
+      <c r="O84" s="7"/>
+      <c r="P84" s="7"/>
+      <c r="Q84" s="7"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7"/>
+      <c r="M85" s="7"/>
+      <c r="N85" s="7"/>
+      <c r="O85" s="7"/>
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
+      <c r="M86" s="7"/>
+      <c r="N86" s="7"/>
+      <c r="O86" s="7"/>
+      <c r="P86" s="7"/>
+      <c r="Q86" s="7"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
+      <c r="M87" s="7"/>
+      <c r="N87" s="7"/>
+      <c r="O87" s="7"/>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="7"/>
+      <c r="K88" s="7"/>
+      <c r="L88" s="7"/>
+      <c r="M88" s="7"/>
+      <c r="N88" s="7"/>
+      <c r="O88" s="7"/>
+      <c r="P88" s="7"/>
+      <c r="Q88" s="7"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+      <c r="J89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7"/>
+      <c r="M89" s="7"/>
+      <c r="N89" s="7"/>
+      <c r="O89" s="7"/>
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7"/>
+      <c r="M90" s="7"/>
+      <c r="N90" s="7"/>
+      <c r="O90" s="7"/>
+      <c r="P90" s="7"/>
+      <c r="Q90" s="7"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
+      <c r="M91" s="7"/>
+      <c r="N91" s="7"/>
+      <c r="O91" s="7"/>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
+      <c r="M92" s="7"/>
+      <c r="N92" s="7"/>
+      <c r="O92" s="7"/>
+      <c r="P92" s="7"/>
+      <c r="Q92" s="7"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
+      <c r="N93" s="7"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
+      <c r="M94" s="7"/>
+      <c r="N94" s="7"/>
+      <c r="O94" s="7"/>
+      <c r="P94" s="7"/>
+      <c r="Q94" s="7"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
+      <c r="M95" s="7"/>
+      <c r="N95" s="7"/>
+      <c r="O95" s="7"/>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="7"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="7"/>
+      <c r="N96" s="7"/>
+      <c r="O96" s="7"/>
+      <c r="P96" s="7"/>
+      <c r="Q96" s="7"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="7"/>
+      <c r="L97" s="7"/>
+      <c r="M97" s="7"/>
+      <c r="N97" s="7"/>
+      <c r="O97" s="7"/>
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="7"/>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="7"/>
+      <c r="P98" s="7"/>
+      <c r="Q98" s="7"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="7"/>
+      <c r="M99" s="7"/>
+      <c r="N99" s="7"/>
+      <c r="O99" s="7"/>
+      <c r="P99" s="7"/>
+      <c r="Q99" s="7"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="7"/>
+      <c r="L100" s="7"/>
+      <c r="M100" s="7"/>
+      <c r="N100" s="7"/>
+      <c r="O100" s="7"/>
+      <c r="P100" s="7"/>
+      <c r="Q100" s="7"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
+      <c r="M101" s="7"/>
+      <c r="N101" s="7"/>
+      <c r="O101" s="7"/>
+      <c r="P101" s="7"/>
+      <c r="Q101" s="7"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" s="7"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7"/>
+      <c r="M102" s="7"/>
+      <c r="N102" s="7"/>
+      <c r="O102" s="7"/>
+      <c r="P102" s="7"/>
+      <c r="Q102" s="7"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7"/>
+      <c r="M103" s="7"/>
+      <c r="N103" s="7"/>
+      <c r="O103" s="7"/>
+      <c r="P103" s="7"/>
+      <c r="Q103" s="7"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="7"/>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7"/>
+      <c r="M104" s="7"/>
+      <c r="N104" s="7"/>
+      <c r="O104" s="7"/>
+      <c r="P104" s="7"/>
+      <c r="Q104" s="7"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
+      <c r="M105" s="7"/>
+      <c r="N105" s="7"/>
+      <c r="O105" s="7"/>
+      <c r="P105" s="7"/>
+      <c r="Q105" s="7"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
+      <c r="K106" s="7"/>
+      <c r="L106" s="7"/>
+      <c r="M106" s="7"/>
+      <c r="N106" s="7"/>
+      <c r="O106" s="7"/>
+      <c r="P106" s="7"/>
+      <c r="Q106" s="7"/>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="7"/>
+      <c r="J107" s="7"/>
+      <c r="K107" s="7"/>
+      <c r="L107" s="7"/>
+      <c r="M107" s="7"/>
+      <c r="N107" s="7"/>
+      <c r="O107" s="7"/>
+      <c r="P107" s="7"/>
+      <c r="Q107" s="7"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="7"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7"/>
+      <c r="M108" s="7"/>
+      <c r="N108" s="7"/>
+      <c r="O108" s="7"/>
+      <c r="P108" s="7"/>
+      <c r="Q108" s="7"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="7"/>
+      <c r="M109" s="7"/>
+      <c r="N109" s="7"/>
+      <c r="O109" s="7"/>
+      <c r="P109" s="7"/>
+      <c r="Q109" s="7"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="7"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="7"/>
+      <c r="J110" s="7"/>
+      <c r="K110" s="7"/>
+      <c r="L110" s="7"/>
+      <c r="M110" s="7"/>
+      <c r="N110" s="7"/>
+      <c r="O110" s="7"/>
+      <c r="P110" s="7"/>
+      <c r="Q110" s="7"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" s="7"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="7"/>
+      <c r="M111" s="7"/>
+      <c r="N111" s="7"/>
+      <c r="O111" s="7"/>
+      <c r="P111" s="7"/>
+      <c r="Q111" s="7"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
+      <c r="K112" s="7"/>
+      <c r="L112" s="7"/>
+      <c r="M112" s="7"/>
+      <c r="N112" s="7"/>
+      <c r="O112" s="7"/>
+      <c r="P112" s="7"/>
+      <c r="Q112" s="7"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="7"/>
+      <c r="N113" s="7"/>
+      <c r="O113" s="7"/>
+      <c r="P113" s="7"/>
+      <c r="Q113" s="7"/>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" s="7"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
+      <c r="M114" s="7"/>
+      <c r="N114" s="7"/>
+      <c r="O114" s="7"/>
+      <c r="P114" s="7"/>
+      <c r="Q114" s="7"/>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115" s="7"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="7"/>
+      <c r="K115" s="7"/>
+      <c r="L115" s="7"/>
+      <c r="M115" s="7"/>
+      <c r="N115" s="7"/>
+      <c r="O115" s="7"/>
+      <c r="P115" s="7"/>
+      <c r="Q115" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q46"/>
+    <mergeCell ref="A1:Q115"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2522,88 +6361,82 @@
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
-      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -2628,15 +6461,9 @@
       <c r="Y2" s="5"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -2661,15 +6488,9 @@
       <c r="Y3" s="5"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -2694,15 +6515,9 @@
       <c r="Y4" s="5"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -2727,15 +6542,9 @@
       <c r="Y5" s="5"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -2760,15 +6569,9 @@
       <c r="Y6" s="5"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -2793,15 +6596,9 @@
       <c r="Y7" s="5"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -2826,15 +6623,9 @@
       <c r="Y8" s="5"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -2859,15 +6650,9 @@
       <c r="Y9" s="5"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -2892,15 +6677,9 @@
       <c r="Y10" s="5"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -2925,15 +6704,9 @@
       <c r="Y11" s="5"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -2958,15 +6731,9 @@
       <c r="Y12" s="5"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -2991,15 +6758,9 @@
       <c r="Y13" s="5"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -3024,15 +6785,9 @@
       <c r="Y14" s="5"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -3057,15 +6812,9 @@
       <c r="Y15" s="5"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -3090,15 +6839,9 @@
       <c r="Y16" s="5"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -3123,15 +6866,9 @@
       <c r="Y17" s="5"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="6">
-        <v>22</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -3156,15 +6893,9 @@
       <c r="Y18" s="5"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="6">
-        <v>22</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -3189,15 +6920,9 @@
       <c r="Y19" s="5"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="6">
-        <v>22</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -3222,15 +6947,9 @@
       <c r="Y20" s="5"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="6">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -3255,15 +6974,9 @@
       <c r="Y21" s="5"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="6">
-        <v>25</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -3288,15 +7001,9 @@
       <c r="Y22" s="5"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="6">
-        <v>25</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -3321,15 +7028,9 @@
       <c r="Y23" s="5"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="6">
-        <v>26</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3354,15 +7055,9 @@
       <c r="Y24" s="5"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="6">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -3387,15 +7082,9 @@
       <c r="Y25" s="5"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="6">
-        <v>30</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -3420,15 +7109,9 @@
       <c r="Y26" s="5"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="6">
-        <v>30</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -3453,15 +7136,9 @@
       <c r="Y27" s="5"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="6">
-        <v>30</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -3486,15 +7163,9 @@
       <c r="Y28" s="5"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="6">
-        <v>30</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -3519,15 +7190,9 @@
       <c r="Y29" s="5"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="6">
-        <v>30</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -3552,15 +7217,9 @@
       <c r="Y30" s="5"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="6">
-        <v>30</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -3585,15 +7244,9 @@
       <c r="Y31" s="5"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="6">
-        <v>33</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -3618,15 +7271,9 @@
       <c r="Y32" s="5"/>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="6">
-        <v>33</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -3651,15 +7298,9 @@
       <c r="Y33" s="5"/>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="6">
-        <v>33</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A34" s="5"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -3684,15 +7325,9 @@
       <c r="Y34" s="5"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="6">
-        <v>33</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A35" s="5"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -3717,15 +7352,9 @@
       <c r="Y35" s="5"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" s="6">
-        <v>33</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -3750,15 +7379,9 @@
       <c r="Y36" s="5"/>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="6">
-        <v>33</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A37" s="5"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -3783,15 +7406,9 @@
       <c r="Y37" s="5"/>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="6">
-        <v>37</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -3816,15 +7433,9 @@
       <c r="Y38" s="5"/>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="6">
-        <v>37</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -3849,15 +7460,9 @@
       <c r="Y39" s="5"/>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="6">
-        <v>54</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -3882,15 +7487,9 @@
       <c r="Y40" s="5"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="6">
-        <v>54</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -3915,15 +7514,9 @@
       <c r="Y41" s="5"/>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="6">
-        <v>102</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -3948,15 +7541,9 @@
       <c r="Y42" s="5"/>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="6">
-        <v>102</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -3981,15 +7568,9 @@
       <c r="Y43" s="5"/>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="6">
-        <v>102</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -4014,15 +7595,9 @@
       <c r="Y44" s="5"/>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B45" s="6">
-        <v>102</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -4047,15 +7622,9 @@
       <c r="Y45" s="5"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="6">
-        <v>115</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -4080,15 +7649,9 @@
       <c r="Y46" s="5"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B47" s="6">
-        <v>115</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -4113,15 +7676,9 @@
       <c r="Y47" s="5"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B48" s="6">
-        <v>115</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -4146,15 +7703,9 @@
       <c r="Y48" s="5"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B49" s="6">
-        <v>115</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -4179,15 +7730,9 @@
       <c r="Y49" s="5"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B50" s="6">
-        <v>115</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="A50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -4212,15 +7757,9 @@
       <c r="Y50" s="5"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="6">
-        <v>115</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="A51" s="5"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>

--- a/Workflows/Chemical validation/Level0_Templates/XXXX_XX_CATIONS.xlsx
+++ b/Workflows/Chemical validation/Level0_Templates/XXXX_XX_CATIONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\Level0_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F350EEA7-2332-4349-BC0B-231B3D58352C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B5029A-6503-4F19-A791-7A367D6EEA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
   </bookViews>
@@ -597,7 +597,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
+            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code could combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
           </a:r>
           <a:endParaRPr lang="es-ES">
             <a:effectLst/>
@@ -721,16 +721,28 @@
             <a:t>- How to fill: </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Use the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>You could use </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
           </a:r>
           <a:endParaRPr lang="es-ES">
             <a:effectLst/>
